--- a/data/Noi dung SICK/00 MUC LUC.xlsx
+++ b/data/Noi dung SICK/00 MUC LUC.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3178,11 +3178,7 @@
       <c r="F74" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Thiết bị phân tích khí và bụi</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/air-quality-measuring-devices/c/g407184</t>
@@ -3216,11 +3212,7 @@
       <c r="F75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Thiết bị phân tích khí và bụi</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/digital-analyzer-solutions/c/g284256</t>
@@ -3254,11 +3246,7 @@
       <c r="F76" t="n">
         <v>0</v>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Thiết bị phân tích khí và bụi</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/dust-measuring-devices/c/g54727</t>
@@ -3292,11 +3280,7 @@
       <c r="F77" t="n">
         <v>0</v>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Thiết bị phân tích khí và bụi</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/gas-analyzers/c/g54724</t>
@@ -3330,11 +3314,7 @@
       <c r="F78" t="n">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Thiết bị phân tích khí và bụi</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/smoke-detectors/c/g284260</t>
@@ -3368,11 +3348,7 @@
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Thiết bị phân tích khí và bụi</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/visual-range-measuring-devices/c/g284262</t>
@@ -6408,11 +6384,7 @@
       <c r="F159" t="n">
         <v>56</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
-        </is>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/inductive-proximity-sensors/imx/c/g555781</t>
@@ -7700,11 +7672,7 @@
       <c r="F193" t="n">
         <v>274</v>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
-        </is>
-      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/photoelectric-sensors/w100/c/g184875</t>
@@ -8080,11 +8048,7 @@
       <c r="F203" t="n">
         <v>78</v>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
-        </is>
-      </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/photoelectric-sensors/w250/c/g203757</t>
@@ -8194,11 +8158,7 @@
       <c r="F206" t="n">
         <v>62</v>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
-        </is>
-      </c>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/photoelectric-sensors/w280/c/g204129</t>
@@ -9260,7 +9220,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -9298,7 +9258,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -9336,7 +9296,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -9374,7 +9334,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -9412,7 +9372,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -9714,11 +9674,7 @@
       <c r="F246" t="n">
         <v>0</v>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
-        </is>
-      </c>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/digital-flow-solutions/c/g543722</t>
@@ -9752,11 +9708,7 @@
       <c r="F247" t="n">
         <v>0</v>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
-        </is>
-      </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/flow-measurement-instruments/c/g543714</t>
@@ -9790,11 +9742,7 @@
       <c r="F248" t="n">
         <v>0</v>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
-        </is>
-      </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/flow-metering-systems/c/g472151</t>
@@ -9828,11 +9776,7 @@
       <c r="F249" t="n">
         <v>0</v>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
-        </is>
-      </c>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/flow-meters/c/g543715</t>
@@ -10512,11 +10456,7 @@
       <c r="F267" t="n">
         <v>9</v>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Cảm biến công nghiệp, Cảm biến radar</t>
-        </is>
-      </c>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/lidar-and-radar-sensors/radar-sensors/rms/c/g628337</t>
@@ -11196,11 +11136,7 @@
       <c r="F285" t="n">
         <v>2</v>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
-        </is>
-      </c>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/machine-vision-and-identification/image-based-code-readers/sensingcam-sec200/c/g625244</t>
@@ -13590,11 +13526,7 @@
       <c r="F348" t="n">
         <v>4</v>
       </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>Encoder bộ mã hóa vòng quay</t>
-        </is>
-      </c>
+      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/motion-control-sensors/motor-feedback-systems/ensenm35/c/g623175</t>
@@ -14274,11 +14206,7 @@
       <c r="F366" t="n">
         <v>56</v>
       </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>Bộ kết nối mạng công nghiệp, Đầu nối và cáp</t>
-        </is>
-      </c>
+      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/network-and-connection-technology/connectors-and-cables/power-cables/c/g628391</t>
@@ -15638,11 +15566,7 @@
       <c r="F402" t="n">
         <v>0</v>
       </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
-        </is>
-      </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/other-products/c/g575324</t>
@@ -19402,7 +19326,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Thiết bị an toàn máy, Công tắc an toàn</t>
+          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -19440,7 +19364,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Thiết bị an toàn máy, Công tắc an toàn</t>
+          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -19516,7 +19440,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Thiết bị an toàn máy, Công tắc an toàn</t>
+          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -20808,7 +20732,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -20920,11 +20844,7 @@
       <c r="F541" t="n">
         <v>1</v>
       </c>
-      <c r="G541" t="inlineStr">
-        <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
-        </is>
-      </c>
+      <c r="G541" t="inlineStr"/>
       <c r="H541" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/systems/quality-control-systems/pallet-serialization-system/c/g624914</t>
@@ -21036,7 +20956,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -21074,7 +20994,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -21112,7 +21032,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -21150,7 +21070,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -21264,7 +21184,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -21302,7 +21222,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -21378,7 +21298,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -21416,7 +21336,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -21530,7 +21450,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
+          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">

--- a/data/Noi dung SICK/00 MUC LUC.xlsx
+++ b/data/Noi dung SICK/00 MUC LUC.xlsx
@@ -436,7 +436,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Có TSKT</t>
+          <t>Nguồn thông số</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -520,7 +520,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -892,15 +892,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1158,15 +1158,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1234,15 +1234,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1880,15 +1880,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1956,15 +1956,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3172,13 +3172,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Thiết bị phân tích khí và bụi</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/air-quality-measuring-devices/c/g407184</t>
@@ -3206,13 +3210,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Thiết bị phân tích khí và bụi</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/digital-analyzer-solutions/c/g284256</t>
@@ -3240,13 +3248,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Thiết bị phân tích khí và bụi</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/dust-measuring-devices/c/g54727</t>
@@ -3274,13 +3286,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Thiết bị phân tích khí và bụi</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/gas-analyzers/c/g54724</t>
@@ -3308,13 +3324,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Thiết bị phân tích khí và bụi</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/smoke-detectors/c/g284260</t>
@@ -3342,13 +3362,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Thiết bị phân tích khí và bụi</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/analyzers/visual-range-measuring-devices/c/g284262</t>
@@ -3376,7 +3400,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -3414,7 +3438,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -3452,7 +3476,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -3490,7 +3514,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -3528,7 +3552,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -3566,7 +3590,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -3604,7 +3628,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3642,7 +3666,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3680,7 +3704,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3718,7 +3742,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3756,7 +3780,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3794,7 +3818,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3832,7 +3856,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3870,7 +3894,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3908,7 +3932,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3946,7 +3970,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3984,7 +4008,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3992,7 +4016,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4022,7 +4046,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -4060,7 +4084,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -4098,7 +4122,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -4136,7 +4160,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4174,7 +4198,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -4212,7 +4236,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -4250,7 +4274,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -4288,7 +4312,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -4326,7 +4350,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -4364,7 +4388,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4402,7 +4426,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -4440,7 +4464,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4478,7 +4502,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -4516,7 +4540,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4554,7 +4578,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -4592,7 +4616,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -4630,7 +4654,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -4668,7 +4692,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -4706,7 +4730,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4744,7 +4768,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -4782,7 +4806,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -4820,7 +4844,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -4858,7 +4882,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4896,7 +4920,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4934,7 +4958,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4972,7 +4996,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -5010,7 +5034,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -5048,7 +5072,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -5086,7 +5110,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -5124,7 +5148,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -5162,7 +5186,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -5200,7 +5224,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -5238,7 +5262,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -5276,7 +5300,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -5314,7 +5338,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -5352,7 +5376,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -5390,7 +5414,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -5428,7 +5452,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -5466,7 +5490,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -5504,7 +5528,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -5542,7 +5566,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -5580,7 +5604,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -5618,7 +5642,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -5656,7 +5680,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -5694,7 +5718,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -5732,7 +5756,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -5770,7 +5794,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -5808,7 +5832,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -5816,7 +5840,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến màu và tương phản</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5846,7 +5870,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -5884,7 +5908,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -5922,7 +5946,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -5960,7 +5984,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -5998,7 +6022,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -6036,7 +6060,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -6074,7 +6098,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -6112,7 +6136,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -6150,7 +6174,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -6188,7 +6212,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -6226,7 +6250,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -6264,7 +6288,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -6302,7 +6326,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -6340,7 +6364,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -6378,13 +6402,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F159" t="n">
         <v>56</v>
       </c>
-      <c r="G159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/inductive-proximity-sensors/imx/c/g555781</t>
@@ -6412,7 +6440,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -6450,7 +6478,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -6488,7 +6516,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -6526,7 +6554,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -6564,7 +6592,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -6602,7 +6630,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -6640,7 +6668,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -6678,7 +6706,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -6716,7 +6744,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -6724,7 +6752,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6754,7 +6782,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -6762,7 +6790,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6792,7 +6820,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -6800,7 +6828,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6830,7 +6858,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -6838,7 +6866,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6868,7 +6896,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -6876,7 +6904,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -6906,7 +6934,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -6914,7 +6942,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6944,7 +6972,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -6952,7 +6980,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -6982,7 +7010,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -6990,7 +7018,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7020,7 +7048,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -7028,7 +7056,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7058,7 +7086,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -7066,7 +7094,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -7096,7 +7124,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -7104,7 +7132,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Cảm biến công nghiệp</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -7134,7 +7162,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -7172,7 +7200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -7210,7 +7238,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -7248,7 +7276,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -7286,7 +7314,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -7324,7 +7352,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -7362,11 +7390,11 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -7400,7 +7428,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -7438,7 +7466,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -7476,7 +7504,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -7514,7 +7542,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -7552,7 +7580,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -7590,7 +7618,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -7628,7 +7656,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -7666,13 +7694,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F193" t="n">
         <v>274</v>
       </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/photoelectric-sensors/w100/c/g184875</t>
@@ -7700,7 +7732,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -7738,7 +7770,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -7776,7 +7808,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -7814,7 +7846,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -7852,7 +7884,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -7890,7 +7922,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -7928,7 +7960,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -7966,11 +7998,11 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -8004,7 +8036,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -8042,13 +8074,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F203" t="n">
         <v>78</v>
       </c>
-      <c r="G203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+        </is>
+      </c>
       <c r="H203" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/photoelectric-sensors/w250/c/g203757</t>
@@ -8076,7 +8112,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -8114,7 +8150,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -8152,13 +8188,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F206" t="n">
         <v>62</v>
       </c>
-      <c r="G206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+        </is>
+      </c>
       <c r="H206" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/detection-sensors/photoelectric-sensors/w280/c/g204129</t>
@@ -8186,7 +8226,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -8224,7 +8264,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -8262,7 +8302,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -8300,7 +8340,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -8338,7 +8378,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -8376,7 +8416,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -8414,7 +8454,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -8452,7 +8492,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -8490,7 +8530,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -8528,7 +8568,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F216" t="n">
@@ -8566,7 +8606,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -8604,7 +8644,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -8642,7 +8682,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F219" t="n">
@@ -8680,7 +8720,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F220" t="n">
@@ -8718,7 +8758,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F221" t="n">
@@ -8756,7 +8796,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -8794,7 +8834,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -8832,7 +8872,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F224" t="n">
@@ -8870,7 +8910,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -8908,7 +8948,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -8946,7 +8986,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -8984,7 +9024,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -9022,7 +9062,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -9060,7 +9100,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -9098,7 +9138,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -9136,7 +9176,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F232" t="n">
@@ -9174,7 +9214,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F233" t="n">
@@ -9212,7 +9252,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -9220,7 +9260,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -9250,7 +9290,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -9258,7 +9298,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -9288,7 +9328,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -9296,7 +9336,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -9326,7 +9366,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F237" t="n">
@@ -9334,7 +9374,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -9364,7 +9404,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F238" t="n">
@@ -9372,7 +9412,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến đo khoảng cách</t>
+          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -9402,7 +9442,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -9440,7 +9480,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F240" t="n">
@@ -9478,7 +9518,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -9516,7 +9556,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F242" t="n">
@@ -9554,7 +9594,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -9592,7 +9632,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -9630,7 +9670,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -9668,13 +9708,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F246" t="n">
         <v>0</v>
       </c>
-      <c r="G246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
+        </is>
+      </c>
       <c r="H246" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/digital-flow-solutions/c/g543722</t>
@@ -9702,13 +9746,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F247" t="n">
         <v>0</v>
       </c>
-      <c r="G247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
+        </is>
+      </c>
       <c r="H247" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/flow-measurement-instruments/c/g543714</t>
@@ -9736,13 +9784,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F248" t="n">
         <v>0</v>
       </c>
-      <c r="G248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
+        </is>
+      </c>
       <c r="H248" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/flow-metering-systems/c/g472151</t>
@@ -9770,13 +9822,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F249" t="n">
         <v>0</v>
       </c>
-      <c r="G249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến lưu lượng</t>
+        </is>
+      </c>
       <c r="H249" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/flow-measurement/flow-meters/c/g543715</t>
@@ -9804,7 +9860,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -9842,7 +9898,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -9880,7 +9936,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -9918,7 +9974,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -9956,7 +10012,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -9994,7 +10050,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -10032,7 +10088,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -10070,7 +10126,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -10108,7 +10164,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -10146,7 +10202,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -10184,7 +10240,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -10222,7 +10278,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -10260,7 +10316,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -10298,7 +10354,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -10336,7 +10392,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F264" t="n">
@@ -10374,7 +10430,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -10412,7 +10468,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -10450,13 +10506,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F267" t="n">
         <v>9</v>
       </c>
-      <c r="G267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Cảm biến công nghiệp, Cảm biến radar</t>
+        </is>
+      </c>
       <c r="H267" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/lidar-and-radar-sensors/radar-sensors/rms/c/g628337</t>
@@ -10484,7 +10544,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -10522,7 +10582,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -10560,7 +10620,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -10598,7 +10658,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -10636,7 +10696,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -10674,7 +10734,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -10712,7 +10772,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -10750,7 +10810,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -10788,7 +10848,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -10796,7 +10856,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -10826,7 +10886,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -10834,7 +10894,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -10864,7 +10924,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -10872,7 +10932,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -10902,7 +10962,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -10910,7 +10970,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -10940,7 +11000,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -10948,7 +11008,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -10978,7 +11038,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -10986,7 +11046,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -11016,7 +11076,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -11024,7 +11084,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -11054,7 +11114,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -11062,7 +11122,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -11092,7 +11152,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -11100,7 +11160,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -11130,13 +11190,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F285" t="n">
         <v>2</v>
       </c>
-      <c r="G285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
+        </is>
+      </c>
       <c r="H285" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/machine-vision-and-identification/image-based-code-readers/sensingcam-sec200/c/g625244</t>
@@ -11164,7 +11228,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -11202,7 +11266,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -11240,7 +11304,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -11278,7 +11342,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -11316,7 +11380,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -11354,7 +11418,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -11392,7 +11456,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F292" t="n">
@@ -11430,7 +11494,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -11468,7 +11532,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -11506,7 +11570,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -11544,7 +11608,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -11582,7 +11646,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -11620,7 +11684,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -11658,7 +11722,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -11696,7 +11760,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -11734,7 +11798,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -11772,7 +11836,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -11810,7 +11874,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -11848,7 +11912,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -11886,7 +11950,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -11924,7 +11988,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -11962,7 +12026,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -12000,7 +12064,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -12038,7 +12102,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -12076,7 +12140,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -12114,7 +12178,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -12152,7 +12216,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -12190,7 +12254,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -12228,7 +12292,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -12266,7 +12330,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -12304,7 +12368,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -12342,7 +12406,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -12380,7 +12444,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -12418,7 +12482,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -12456,7 +12520,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -12494,7 +12558,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F321" t="n">
@@ -12532,7 +12596,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F322" t="n">
@@ -12570,7 +12634,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F323" t="n">
@@ -12608,7 +12672,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -12646,7 +12710,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -12684,7 +12748,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -12722,7 +12786,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -12760,7 +12824,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -12798,7 +12862,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -12836,7 +12900,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -12874,7 +12938,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -12912,7 +12976,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -12950,7 +13014,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -12988,7 +13052,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -13026,7 +13090,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -13064,7 +13128,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -13102,7 +13166,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F337" t="n">
@@ -13140,7 +13204,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -13178,7 +13242,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F339" t="n">
@@ -13216,7 +13280,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -13254,7 +13318,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -13292,7 +13356,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -13330,7 +13394,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -13368,7 +13432,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -13376,7 +13440,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -13406,7 +13470,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -13414,7 +13478,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -13444,7 +13508,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F346" t="n">
@@ -13482,7 +13546,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F347" t="n">
@@ -13490,7 +13554,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -13520,13 +13584,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F348" t="n">
         <v>4</v>
       </c>
-      <c r="G348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Encoder bộ mã hóa vòng quay</t>
+        </is>
+      </c>
       <c r="H348" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/motion-control-sensors/motor-feedback-systems/ensenm35/c/g623175</t>
@@ -13554,7 +13622,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F349" t="n">
@@ -13592,7 +13660,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -13600,7 +13668,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -13630,7 +13698,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F351" t="n">
@@ -13668,7 +13736,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F352" t="n">
@@ -13706,7 +13774,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -13744,7 +13812,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -13782,7 +13850,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -13820,7 +13888,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -13828,7 +13896,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -13858,7 +13926,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F357" t="n">
@@ -13896,7 +13964,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F358" t="n">
@@ -13934,7 +14002,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F359" t="n">
@@ -13972,7 +14040,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F360" t="n">
@@ -14010,7 +14078,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F361" t="n">
@@ -14048,7 +14116,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F362" t="n">
@@ -14086,7 +14154,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F363" t="n">
@@ -14124,7 +14192,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F364" t="n">
@@ -14162,7 +14230,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F365" t="n">
@@ -14200,13 +14268,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F366" t="n">
         <v>56</v>
       </c>
-      <c r="G366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Bộ kết nối mạng công nghiệp, Đầu nối và cáp</t>
+        </is>
+      </c>
       <c r="H366" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/network-and-connection-technology/connectors-and-cables/power-cables/c/g628391</t>
@@ -14234,7 +14306,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F367" t="n">
@@ -14272,7 +14344,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F368" t="n">
@@ -14310,7 +14382,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -14348,7 +14420,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -14386,7 +14458,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -14424,7 +14496,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -14462,7 +14534,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -14500,7 +14572,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -14538,7 +14610,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -14576,7 +14648,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -14614,7 +14686,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -14652,7 +14724,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -14690,7 +14762,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -14728,7 +14800,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -14766,7 +14838,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -14804,7 +14876,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F382" t="n">
@@ -14842,7 +14914,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F383" t="n">
@@ -14880,7 +14952,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F384" t="n">
@@ -14918,7 +14990,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F385" t="n">
@@ -14956,7 +15028,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F386" t="n">
@@ -14994,7 +15066,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F387" t="n">
@@ -15032,7 +15104,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F388" t="n">
@@ -15070,7 +15142,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F389" t="n">
@@ -15108,7 +15180,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F390" t="n">
@@ -15146,7 +15218,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F391" t="n">
@@ -15184,7 +15256,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F392" t="n">
@@ -15222,7 +15294,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F393" t="n">
@@ -15260,7 +15332,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -15298,7 +15370,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -15336,7 +15408,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -15374,7 +15446,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -15412,7 +15484,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -15450,7 +15522,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F399" t="n">
@@ -15488,7 +15560,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F400" t="n">
@@ -15526,7 +15598,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F401" t="n">
@@ -15562,11 +15634,19 @@
           <t>x</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
       <c r="F402" t="n">
         <v>0</v>
       </c>
-      <c r="G402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+        </is>
+      </c>
       <c r="H402" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/other-products/c/g575324</t>
@@ -15594,7 +15674,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F403" t="n">
@@ -15632,7 +15712,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F404" t="n">
@@ -15670,7 +15750,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F405" t="n">
@@ -15708,7 +15788,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F406" t="n">
@@ -15746,7 +15826,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F407" t="n">
@@ -15784,7 +15864,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -15822,7 +15902,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -15860,7 +15940,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -15898,7 +15978,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -15936,7 +16016,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -15974,7 +16054,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -16012,7 +16092,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -16050,7 +16130,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -16088,7 +16168,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -16126,7 +16206,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -16164,7 +16244,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F418" t="n">
@@ -16202,7 +16282,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F419" t="n">
@@ -16240,7 +16320,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F420" t="n">
@@ -16278,7 +16358,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F421" t="n">
@@ -16316,7 +16396,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -16354,7 +16434,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -16392,7 +16472,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -16430,7 +16510,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -16468,7 +16548,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -16506,7 +16586,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -16544,7 +16624,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -16582,7 +16662,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -16620,7 +16700,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -16658,7 +16738,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -16696,7 +16776,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -16734,7 +16814,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -16772,7 +16852,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -16810,7 +16890,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -16848,7 +16928,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -16886,7 +16966,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -16894,7 +16974,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -16924,7 +17004,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F438" t="n">
@@ -16932,7 +17012,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -16962,7 +17042,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F439" t="n">
@@ -16970,7 +17050,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -17000,7 +17080,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F440" t="n">
@@ -17008,7 +17088,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -17038,7 +17118,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F441" t="n">
@@ -17046,7 +17126,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -17076,7 +17156,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F442" t="n">
@@ -17084,7 +17164,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -17114,7 +17194,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F443" t="n">
@@ -17122,7 +17202,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -17152,7 +17232,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F444" t="n">
@@ -17160,7 +17240,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyệt đối</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -17190,7 +17270,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F445" t="n">
@@ -17198,7 +17278,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Encoder bộ mã hóa vòng quay, Encoder tuyến tính</t>
+          <t>Encoder bộ mã hóa vòng quay</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -17228,7 +17308,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -17266,7 +17346,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -17304,7 +17384,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -17342,7 +17422,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -17380,7 +17460,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -17418,7 +17498,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -17456,7 +17536,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -17494,7 +17574,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -17532,7 +17612,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -17570,7 +17650,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F455" t="n">
@@ -17608,7 +17688,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -17646,7 +17726,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -17684,7 +17764,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -17722,7 +17802,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F459" t="n">
@@ -17760,7 +17840,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F460" t="n">
@@ -17798,7 +17878,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F461" t="n">
@@ -17836,7 +17916,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F462" t="n">
@@ -17874,7 +17954,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F463" t="n">
@@ -17912,7 +17992,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F464" t="n">
@@ -17950,7 +18030,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F465" t="n">
@@ -17988,7 +18068,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F466" t="n">
@@ -18026,11 +18106,11 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F467" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -18064,7 +18144,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F468" t="n">
@@ -18102,7 +18182,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F469" t="n">
@@ -18140,7 +18220,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F470" t="n">
@@ -18148,7 +18228,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Thiết bị an toàn máy, Lưới quang an toàn</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -18178,7 +18258,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F471" t="n">
@@ -18186,7 +18266,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Thiết bị an toàn máy, Lưới quang an toàn</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -18216,7 +18296,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -18224,7 +18304,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Thiết bị an toàn máy, Lưới quang an toàn</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -18254,7 +18334,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -18262,7 +18342,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Thiết bị an toàn máy, Lưới quang an toàn</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -18292,7 +18372,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -18330,7 +18410,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -18338,7 +18418,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến quang điện</t>
+          <t>Thiết bị an toàn máy, Lưới quang an toàn</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -18368,7 +18448,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -18376,7 +18456,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến dạng fork</t>
+          <t>Thiết bị an toàn máy, Lưới quang an toàn</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -18406,7 +18486,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -18444,7 +18524,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -18482,7 +18562,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -18520,7 +18600,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -18558,7 +18638,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -18596,7 +18676,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F482" t="n">
@@ -18634,7 +18714,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F483" t="n">
@@ -18672,7 +18752,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F484" t="n">
@@ -18710,7 +18790,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F485" t="n">
@@ -18748,7 +18828,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F486" t="n">
@@ -18786,7 +18866,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F487" t="n">
@@ -18824,7 +18904,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F488" t="n">
@@ -18862,7 +18942,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F489" t="n">
@@ -18900,7 +18980,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -18938,7 +19018,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -18976,7 +19056,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F492" t="n">
@@ -19014,7 +19094,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F493" t="n">
@@ -19052,7 +19132,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F494" t="n">
@@ -19090,7 +19170,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F495" t="n">
@@ -19128,7 +19208,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F496" t="n">
@@ -19166,7 +19246,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -19204,7 +19284,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F498" t="n">
@@ -19242,7 +19322,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -19280,7 +19360,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -19318,7 +19398,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -19326,7 +19406,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Thiết bị an toàn máy, Công tắc an toàn</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -19356,7 +19436,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -19364,7 +19444,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Thiết bị an toàn máy, Công tắc an toàn</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -19394,7 +19474,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -19432,7 +19512,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -19440,7 +19520,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Cảm biến công nghiệp, Cảm biến tiệm cận</t>
+          <t>Thiết bị an toàn máy, Công tắc an toàn</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -19470,7 +19550,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -19508,7 +19588,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -19546,7 +19626,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F507" t="n">
@@ -19584,7 +19664,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F508" t="n">
@@ -19622,7 +19702,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F509" t="n">
@@ -19660,7 +19740,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F510" t="n">
@@ -19698,7 +19778,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F511" t="n">
@@ -19736,7 +19816,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F512" t="n">
@@ -19774,7 +19854,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F513" t="n">
@@ -19812,7 +19892,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F514" t="n">
@@ -19850,7 +19930,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>(không có)</t>
         </is>
       </c>
       <c r="F515" t="n">
@@ -19888,7 +19968,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F516" t="n">
@@ -19926,7 +20006,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F517" t="n">
@@ -19964,7 +20044,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F518" t="n">
@@ -20002,7 +20082,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F519" t="n">
@@ -20040,7 +20120,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F520" t="n">
@@ -20048,7 +20128,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -20078,7 +20158,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -20086,7 +20166,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -20116,7 +20196,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F522" t="n">
@@ -20124,7 +20204,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -20154,7 +20234,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F523" t="n">
@@ -20162,7 +20242,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -20192,7 +20272,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F524" t="n">
@@ -20200,7 +20280,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -20230,7 +20310,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F525" t="n">
@@ -20238,7 +20318,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -20268,7 +20348,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F526" t="n">
@@ -20276,7 +20356,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -20306,7 +20386,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F527" t="n">
@@ -20314,7 +20394,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -20344,7 +20424,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F528" t="n">
@@ -20352,7 +20432,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -20382,7 +20462,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F529" t="n">
@@ -20390,7 +20470,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -20420,7 +20500,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F530" t="n">
@@ -20428,7 +20508,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -20458,7 +20538,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F531" t="n">
@@ -20466,7 +20546,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -20496,7 +20576,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F532" t="n">
@@ -20504,7 +20584,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -20534,7 +20614,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F533" t="n">
@@ -20542,7 +20622,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -20572,7 +20652,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F534" t="n">
@@ -20580,7 +20660,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -20610,7 +20690,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F535" t="n">
@@ -20618,7 +20698,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -20648,7 +20728,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F536" t="n">
@@ -20656,7 +20736,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -20686,7 +20766,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F537" t="n">
@@ -20694,7 +20774,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -20724,7 +20804,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F538" t="n">
@@ -20732,12 +20812,12 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>https://www.sick.com/sg/en/catalog/archive/label-checker/c/g499551</t>
+          <t>https://www.sick.com/sg/en/catalog/products/systems/quality-control-systems/label-checker/c/g499551</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20842,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F539" t="n">
@@ -20770,7 +20850,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -20800,7 +20880,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F540" t="n">
@@ -20808,7 +20888,7 @@
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -20838,13 +20918,17 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F541" t="n">
         <v>1</v>
       </c>
-      <c r="G541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+        </is>
+      </c>
       <c r="H541" t="inlineStr">
         <is>
           <t>https://www.sick.com/sg/en/catalog/products/systems/quality-control-systems/pallet-serialization-system/c/g624914</t>
@@ -20872,7 +20956,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F542" t="n">
@@ -20880,7 +20964,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -20910,7 +20994,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F543" t="n">
@@ -20918,7 +21002,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -20948,7 +21032,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F544" t="n">
@@ -20956,7 +21040,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -20986,7 +21070,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F545" t="n">
@@ -20994,7 +21078,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -21024,7 +21108,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F546" t="n">
@@ -21032,7 +21116,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -21062,7 +21146,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -21070,7 +21154,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -21100,7 +21184,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -21108,7 +21192,7 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -21138,7 +21222,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F549" t="n">
@@ -21146,7 +21230,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -21176,7 +21260,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F550" t="n">
@@ -21184,7 +21268,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Camera công nghiệp 2D/3D</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -21214,7 +21298,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -21222,7 +21306,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -21252,7 +21336,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F552" t="n">
@@ -21260,7 +21344,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -21290,7 +21374,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -21298,7 +21382,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -21328,7 +21412,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F554" t="n">
@@ -21336,7 +21420,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Máy đọc mã vạch</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -21366,15 +21450,15 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Bảng mã ở Variants</t>
         </is>
       </c>
       <c r="F555" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -21404,7 +21488,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F556" t="n">
@@ -21412,7 +21496,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -21442,7 +21526,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F557" t="n">
@@ -21450,7 +21534,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Vision và Nhận dạng, Đầu đọc RFID</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -21480,7 +21564,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F558" t="n">
@@ -21488,7 +21572,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -21518,7 +21602,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F559" t="n">
@@ -21526,7 +21610,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -21556,7 +21640,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F560" t="n">
@@ -21564,7 +21648,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -21594,7 +21678,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Technical data overview</t>
         </is>
       </c>
       <c r="F561" t="n">
@@ -21602,7 +21686,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Không có danh mục sản phẩm,  chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
+          <t>Không có danh mục sản phẩm, chỉ nằm trong danh mục Thương Hiệu SICK Sensor</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
